--- a/hall/resources/sample/SeasonStart.xlsx
+++ b/hall/resources/sample/SeasonStart.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <si>
     <t>活动ID</t>
   </si>
@@ -50,6 +50,9 @@
     <t>循环的序列</t>
   </si>
   <si>
+    <t>赛季名称备选</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -77,31 +80,483 @@
     <t>进阶赛季</t>
   </si>
   <si>
-    <t>金钱兔</t>
-  </si>
-  <si>
-    <t>金蛇赛季</t>
-  </si>
-  <si>
-    <t>金蛇招财</t>
-  </si>
-  <si>
-    <t>金钱赛季</t>
-  </si>
-  <si>
-    <t>财富银行</t>
-  </si>
-  <si>
-    <t>赛博赛季</t>
-  </si>
-  <si>
     <t>蒸汽时代</t>
   </si>
   <si>
-    <t>体育赛季</t>
-  </si>
-  <si>
-    <t>篮球巨星</t>
+    <t>神域对决赛季</t>
+  </si>
+  <si>
+    <t>宙斯VS哈迪斯</t>
+  </si>
+  <si>
+    <r>
+      <t>神域纷争</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>诸神黄昏</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>神王之怒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>天庭裂变</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>圣战纪元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>众神裁决</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>神域对决</t>
+    </r>
+  </si>
+  <si>
+    <t>黑帆远征赛季</t>
+  </si>
+  <si>
+    <t>杰克船长</t>
+  </si>
+  <si>
+    <r>
+      <t>黑帆远征</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>怒海争锋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>加勒比暗潮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>航海霸业</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>海盗法则</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>深渊掠夺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>怒海狂潮</t>
+    </r>
+  </si>
+  <si>
+    <t>血月狼影赛季</t>
+  </si>
+  <si>
+    <t>狼月</t>
+  </si>
+  <si>
+    <r>
+      <t>暗月狂嚎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>狼嚎之夜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>血月猎杀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>变身之月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>狼族觉醒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>月蚀猎场</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>血月狼影</t>
+    </r>
+  </si>
+  <si>
+    <t>浩克狂潮赛季</t>
+  </si>
+  <si>
+    <t>绿巨人</t>
+  </si>
+  <si>
+    <r>
+      <t>暴怒觉醒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>狂暴之躯</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>绿殇降临</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碾压纪元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>浩克狂潮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>怒焰破城</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>伽马裂变</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -114,13 +569,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF404040"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -265,6 +726,12 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF404040"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -587,141 +1054,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1249,17 +1719,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="11.375" customWidth="1"/>
     <col min="4" max="4" width="15.875" customWidth="1"/>
     <col min="5" max="5" width="13.625" customWidth="1"/>
     <col min="6" max="6" width="12.625" customWidth="1"/>
     <col min="7" max="7" width="15.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1281,46 +1752,49 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="L1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:12">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1329,7 +1803,7 @@
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:12">
       <c r="A5" s="1">
         <v>1001</v>
       </c>
@@ -1337,7 +1811,7 @@
         <v>4059002</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -1346,11 +1820,11 @@
         <v>100300</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:12">
       <c r="A6" s="1">
         <v>1002</v>
       </c>
@@ -1358,20 +1832,20 @@
         <v>4059094</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
       </c>
-      <c r="E6" s="1">
-        <v>103501</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>16</v>
+      <c r="E6">
+        <v>102300</v>
+      </c>
+      <c r="F6" t="s">
+        <v>17</v>
       </c>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" ht="15.75" spans="1:12">
       <c r="A7" s="1">
         <f t="shared" ref="A7:A10" si="0">1000*10+G7</f>
         <v>10001</v>
@@ -1380,22 +1854,27 @@
         <v>4059191</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" s="1">
         <v>14</v>
       </c>
-      <c r="E7" s="1">
-        <v>103500</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>18</v>
+      <c r="E7">
+        <v>102000</v>
+      </c>
+      <c r="F7" t="s">
+        <v>19</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
       </c>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="L7" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" ht="15.75" spans="1:12">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>10002</v>
@@ -1404,22 +1883,27 @@
         <v>4059192</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D8" s="1">
         <v>14</v>
       </c>
-      <c r="E8" s="1">
-        <v>102400</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>20</v>
+      <c r="E8">
+        <v>102100</v>
+      </c>
+      <c r="F8" t="s">
+        <v>22</v>
       </c>
       <c r="G8" s="1">
         <v>2</v>
       </c>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="L8" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" ht="15.75" spans="1:12">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>10003</v>
@@ -1428,22 +1912,27 @@
         <v>4059193</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D9" s="1">
         <v>14</v>
       </c>
-      <c r="E9" s="1">
-        <v>102300</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>22</v>
+      <c r="E9">
+        <v>101500</v>
+      </c>
+      <c r="F9" t="s">
+        <v>25</v>
       </c>
       <c r="G9" s="1">
         <v>3</v>
       </c>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="L9" s="2" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" ht="15.75" spans="1:12">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>10004</v>
@@ -1452,19 +1941,24 @@
         <v>4059194</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D10" s="1">
         <v>14</v>
       </c>
-      <c r="E10" s="1">
-        <v>101800</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>24</v>
+      <c r="E10">
+        <v>103100</v>
+      </c>
+      <c r="F10" t="s">
+        <v>28</v>
       </c>
       <c r="G10" s="1">
         <v>4</v>
+      </c>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="L10" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/SeasonStart.xlsx
+++ b/hall/resources/sample/SeasonStart.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
   <si>
     <t>活动ID</t>
   </si>
@@ -47,6 +47,9 @@
     <t>备注</t>
   </si>
   <si>
+    <t>开启的宝石孔数</t>
+  </si>
+  <si>
     <t>循环的序列</t>
   </si>
   <si>
@@ -68,6 +71,9 @@
     <t>AvailableGames</t>
   </si>
   <si>
+    <t>GemCount</t>
+  </si>
+  <si>
     <t>LoopSequence</t>
   </si>
   <si>
@@ -90,6 +96,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>神域纷争</t>
     </r>
     <r>
@@ -209,6 +221,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>黑帆远征</t>
     </r>
     <r>
@@ -328,6 +346,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>暗月狂嚎</t>
     </r>
     <r>
@@ -447,6 +471,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>暴怒觉醒</t>
     </r>
     <r>
@@ -1719,7 +1749,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -1727,10 +1757,10 @@
     <col min="4" max="4" width="15.875" customWidth="1"/>
     <col min="5" max="5" width="13.625" customWidth="1"/>
     <col min="6" max="6" width="12.625" customWidth="1"/>
-    <col min="7" max="7" width="15.25" customWidth="1"/>
+    <col min="7" max="8" width="15.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1752,49 +1782,58 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="M1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:13">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1802,8 +1841,9 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:13">
       <c r="A5" s="1">
         <v>1001</v>
       </c>
@@ -1811,7 +1851,7 @@
         <v>4059002</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -1820,11 +1860,14 @@
         <v>100300</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="G5" s="1">
+        <v>3</v>
+      </c>
+      <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:13">
       <c r="A6" s="1">
         <v>1002</v>
       </c>
@@ -1832,7 +1875,7 @@
         <v>4059094</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -1841,20 +1884,23 @@
         <v>102300</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="G6" s="1">
+        <v>6</v>
+      </c>
+      <c r="H6" s="1"/>
     </row>
-    <row r="7" ht="15.75" spans="1:12">
+    <row r="7" ht="15.75" spans="1:13">
       <c r="A7" s="1">
-        <f t="shared" ref="A7:A10" si="0">1000*10+G7</f>
+        <f t="shared" ref="A7:A10" si="0">1000*10+H7</f>
         <v>10001</v>
       </c>
       <c r="B7" s="1">
         <v>4059191</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D7" s="1">
         <v>14</v>
@@ -1863,18 +1909,19 @@
         <v>102000</v>
       </c>
       <c r="F7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G7" s="1">
+        <v>9</v>
+      </c>
+      <c r="H7" s="1">
         <v>1</v>
       </c>
-      <c r="H7"/>
-      <c r="I7"/>
-      <c r="L7" s="2" t="s">
-        <v>20</v>
+      <c r="M7" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="8" ht="15.75" spans="1:12">
+    <row r="8" ht="15.75" spans="1:13">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>10002</v>
@@ -1883,7 +1930,7 @@
         <v>4059192</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D8" s="1">
         <v>14</v>
@@ -1892,18 +1939,19 @@
         <v>102100</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G8" s="1">
+        <v>9</v>
+      </c>
+      <c r="H8" s="1">
         <v>2</v>
       </c>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="L8" s="2" t="s">
-        <v>23</v>
+      <c r="M8" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="9" ht="15.75" spans="1:12">
+    <row r="9" ht="15.75" spans="1:13">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>10003</v>
@@ -1912,7 +1960,7 @@
         <v>4059193</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D9" s="1">
         <v>14</v>
@@ -1921,18 +1969,19 @@
         <v>101500</v>
       </c>
       <c r="F9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G9" s="1">
+        <v>9</v>
+      </c>
+      <c r="H9" s="1">
         <v>3</v>
       </c>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="L9" s="2" t="s">
-        <v>26</v>
+      <c r="M9" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="10" ht="15.75" spans="1:12">
+    <row r="10" ht="15.75" spans="1:13">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>10004</v>
@@ -1941,7 +1990,7 @@
         <v>4059194</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D10" s="1">
         <v>14</v>
@@ -1950,15 +1999,16 @@
         <v>103100</v>
       </c>
       <c r="F10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G10" s="1">
+        <v>9</v>
+      </c>
+      <c r="H10" s="1">
         <v>4</v>
       </c>
-      <c r="H10"/>
-      <c r="I10"/>
-      <c r="L10" s="2" t="s">
-        <v>29</v>
+      <c r="M10" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/SeasonStart.xlsx
+++ b/hall/resources/sample/SeasonStart.xlsx
@@ -26,8 +26,108 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1.万比分，前端显示为百分比；
+2.此值不为对应游戏实际的RTP，只是用于前端显示；</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+此值用于前端显示</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1.用于前端显示；
+2.此值的上限根据赛季玩法的宝石（下注）进行调整，宝石的上限提升后，此值的上限也进行提升，要相互对应</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1.显示多语言，用于前端显示</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="51">
   <si>
     <t>活动ID</t>
   </si>
@@ -53,12 +153,30 @@
     <t>循环的序列</t>
   </si>
   <si>
+    <t>游戏的RTP</t>
+  </si>
+  <si>
+    <t>游戏的最大倍率</t>
+  </si>
+  <si>
+    <t>下注范围</t>
+  </si>
+  <si>
+    <t>特色玩法多语言</t>
+  </si>
+  <si>
+    <t>开启的小游戏</t>
+  </si>
+  <si>
     <t>赛季名称备选</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
+    <t>list&lt;int&gt;{_}</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -77,24 +195,54 @@
     <t>LoopSequence</t>
   </si>
   <si>
+    <t>GameRTP</t>
+  </si>
+  <si>
+    <t>MaxMultiplier</t>
+  </si>
+  <si>
+    <t>BetRange</t>
+  </si>
+  <si>
+    <t>FeatureName</t>
+  </si>
+  <si>
+    <t>Openminigame</t>
+  </si>
+  <si>
     <t>新手赛季</t>
   </si>
   <si>
     <t>超级明星</t>
   </si>
   <si>
+    <t>100_1000</t>
+  </si>
+  <si>
+    <t>单线玩法</t>
+  </si>
+  <si>
     <t>进阶赛季</t>
   </si>
   <si>
     <t>蒸汽时代</t>
   </si>
   <si>
+    <t>拓展转轴</t>
+  </si>
+  <si>
+    <t>300800_400800</t>
+  </si>
+  <si>
     <t>神域对决赛季</t>
   </si>
   <si>
     <t>宙斯VS哈迪斯</t>
   </si>
   <si>
+    <t>扩展百搭</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10.5"/>
@@ -220,6 +368,9 @@
     <t>杰克船长</t>
   </si>
   <si>
+    <t>全线中奖</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10.5"/>
@@ -345,6 +496,9 @@
     <t>狼月</t>
   </si>
   <si>
+    <t>中奖消除</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10.5"/>
@@ -468,6 +622,9 @@
   </si>
   <si>
     <t>绿巨人</t>
+  </si>
+  <si>
+    <t>中奖线玩法</t>
   </si>
   <si>
     <r>
@@ -599,7 +756,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -761,6 +918,17 @@
       <sz val="10.5"/>
       <color rgb="FF404040"/>
       <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1749,7 +1917,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -1758,9 +1926,13 @@
     <col min="5" max="5" width="13.625" customWidth="1"/>
     <col min="6" max="6" width="12.625" customWidth="1"/>
     <col min="7" max="8" width="15.25" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="14.25" customWidth="1"/>
+    <col min="12" max="12" width="15.25" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1785,55 +1957,103 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
       <c r="M1" t="s">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:16">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1843,7 +2063,7 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:16">
       <c r="A5" s="1">
         <v>1001</v>
       </c>
@@ -1851,7 +2071,7 @@
         <v>4059002</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -1860,14 +2080,29 @@
         <v>100300</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G5" s="1">
         <v>3</v>
       </c>
       <c r="H5" s="1"/>
+      <c r="I5">
+        <v>9650</v>
+      </c>
+      <c r="J5">
+        <v>1000</v>
+      </c>
+      <c r="K5" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5">
+        <v>4059215</v>
+      </c>
+      <c r="M5" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:16">
       <c r="A6" s="1">
         <v>1002</v>
       </c>
@@ -1875,7 +2110,7 @@
         <v>4059094</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -1884,14 +2119,32 @@
         <v>102300</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G6" s="1">
         <v>6</v>
       </c>
       <c r="H6" s="1"/>
+      <c r="I6">
+        <v>9700</v>
+      </c>
+      <c r="J6">
+        <v>3300</v>
+      </c>
+      <c r="K6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6">
+        <v>4059216</v>
+      </c>
+      <c r="M6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N6" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="7" ht="15.75" spans="1:13">
+    <row r="7" ht="15.75" spans="1:16">
       <c r="A7" s="1">
         <f t="shared" ref="A7:A10" si="0">1000*10+H7</f>
         <v>10001</v>
@@ -1900,7 +2153,7 @@
         <v>4059191</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D7" s="1">
         <v>14</v>
@@ -1909,7 +2162,7 @@
         <v>102000</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="G7" s="1">
         <v>9</v>
@@ -1917,11 +2170,29 @@
       <c r="H7" s="1">
         <v>1</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>22</v>
+      <c r="I7">
+        <v>9750</v>
+      </c>
+      <c r="J7">
+        <v>1000</v>
+      </c>
+      <c r="K7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7">
+        <v>4059217</v>
+      </c>
+      <c r="M7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N7" t="s">
+        <v>34</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="8" ht="15.75" spans="1:13">
+    <row r="8" ht="15.75" spans="1:16">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>10002</v>
@@ -1930,7 +2201,7 @@
         <v>4059192</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="D8" s="1">
         <v>14</v>
@@ -1939,7 +2210,7 @@
         <v>102100</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G8" s="1">
         <v>9</v>
@@ -1947,11 +2218,29 @@
       <c r="H8" s="1">
         <v>2</v>
       </c>
-      <c r="M8" s="2" t="s">
-        <v>25</v>
+      <c r="I8">
+        <v>9800</v>
+      </c>
+      <c r="J8">
+        <v>2000</v>
+      </c>
+      <c r="K8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L8">
+        <v>4059218</v>
+      </c>
+      <c r="M8" t="s">
+        <v>41</v>
+      </c>
+      <c r="N8" t="s">
+        <v>34</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="9" ht="15.75" spans="1:13">
+    <row r="9" ht="15.75" spans="1:16">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>10003</v>
@@ -1960,7 +2249,7 @@
         <v>4059193</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D9" s="1">
         <v>14</v>
@@ -1969,7 +2258,7 @@
         <v>101500</v>
       </c>
       <c r="F9" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G9" s="1">
         <v>9</v>
@@ -1977,11 +2266,29 @@
       <c r="H9" s="1">
         <v>3</v>
       </c>
-      <c r="M9" s="2" t="s">
-        <v>28</v>
+      <c r="I9">
+        <v>9700</v>
+      </c>
+      <c r="J9">
+        <v>2000</v>
+      </c>
+      <c r="K9" t="s">
+        <v>29</v>
+      </c>
+      <c r="L9">
+        <v>4059219</v>
+      </c>
+      <c r="M9" t="s">
+        <v>45</v>
+      </c>
+      <c r="N9" t="s">
+        <v>34</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="10" ht="15.75" spans="1:13">
+    <row r="10" ht="15.75" spans="1:16">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>10004</v>
@@ -1990,7 +2297,7 @@
         <v>4059194</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D10" s="1">
         <v>14</v>
@@ -1999,7 +2306,7 @@
         <v>103100</v>
       </c>
       <c r="F10" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="G10" s="1">
         <v>9</v>
@@ -2007,12 +2314,31 @@
       <c r="H10" s="1">
         <v>4</v>
       </c>
-      <c r="M10" s="2" t="s">
-        <v>31</v>
+      <c r="I10">
+        <v>9750</v>
+      </c>
+      <c r="J10">
+        <v>2000</v>
+      </c>
+      <c r="K10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L10">
+        <v>4059220</v>
+      </c>
+      <c r="M10" t="s">
+        <v>49</v>
+      </c>
+      <c r="N10" t="s">
+        <v>34</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/hall/resources/sample/SeasonStart.xlsx
+++ b/hall/resources/sample/SeasonStart.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="SeasonStart" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -127,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="63">
   <si>
     <t>活动ID</t>
   </si>
@@ -213,7 +214,7 @@
     <t>新手赛季</t>
   </si>
   <si>
-    <t>超级明星</t>
+    <t>埃及艳后</t>
   </si>
   <si>
     <t>100_1000</t>
@@ -234,6 +235,48 @@
     <t>300800_400800</t>
   </si>
   <si>
+    <t>恶魔之子赛季</t>
+  </si>
+  <si>
+    <t>恶魔之子</t>
+  </si>
+  <si>
+    <t>中奖线玩法</t>
+  </si>
+  <si>
+    <t>暗影降临/地狱之门/血月之约/魔焰重燃</t>
+  </si>
+  <si>
+    <t>雪国狂欢赛季</t>
+  </si>
+  <si>
+    <t>圣诞狂欢夜</t>
+  </si>
+  <si>
+    <t>中奖消除</t>
+  </si>
+  <si>
+    <t>圣诞颂歌/礼物狂潮/冬日盛宴/北极星之愿/圣诞工厂</t>
+  </si>
+  <si>
+    <t>愤怒风暴赛季</t>
+  </si>
+  <si>
+    <t>愤怒的小鸟</t>
+  </si>
+  <si>
+    <t>暴走小鸟季/破壳时刻/复仇纪元/蛋之守护/猪猪末日</t>
+  </si>
+  <si>
+    <t>宝石觉醒赛季</t>
+  </si>
+  <si>
+    <t>伽罗宝石</t>
+  </si>
+  <si>
+    <t>伽罗秘术/伽罗契约/永恒晶石/宝石幻境/魔力宝石季</t>
+  </si>
+  <si>
     <t>神域对决赛季</t>
   </si>
   <si>
@@ -496,9 +539,6 @@
     <t>狼月</t>
   </si>
   <si>
-    <t>中奖消除</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10.5"/>
@@ -622,9 +662,6 @@
   </si>
   <si>
     <t>绿巨人</t>
-  </si>
-  <si>
-    <t>中奖线玩法</t>
   </si>
   <si>
     <r>
@@ -756,7 +793,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -767,6 +804,12 @@
     <font>
       <sz val="10.5"/>
       <color rgb="FF404040"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF171717"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -921,12 +964,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1252,137 +1295,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1390,6 +1433,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2077,9 +2123,9 @@
         <v>3</v>
       </c>
       <c r="E5" s="1">
-        <v>100300</v>
-      </c>
-      <c r="F5" s="1" t="s">
+        <v>101400</v>
+      </c>
+      <c r="F5" t="s">
         <v>28</v>
       </c>
       <c r="G5" s="1">
@@ -2144,22 +2190,22 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" ht="15.75" spans="1:16">
+    <row r="7" spans="1:16">
       <c r="A7" s="1">
-        <f t="shared" ref="A7:A10" si="0">1000*10+H7</f>
+        <f>1000*10+H7</f>
         <v>10001</v>
       </c>
       <c r="B7" s="1">
         <v>4059191</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D7" s="1">
         <v>14</v>
       </c>
       <c r="E7">
-        <v>102000</v>
+        <v>103800</v>
       </c>
       <c r="F7" t="s">
         <v>36</v>
@@ -2180,7 +2226,7 @@
         <v>29</v>
       </c>
       <c r="L7">
-        <v>4059217</v>
+        <v>4059220</v>
       </c>
       <c r="M7" t="s">
         <v>37</v>
@@ -2192,22 +2238,22 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" ht="15.75" spans="1:16">
+    <row r="8" spans="1:16">
       <c r="A8" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A7:A10" si="0">1000*10+H8</f>
         <v>10002</v>
       </c>
       <c r="B8" s="1">
         <v>4059192</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="3" t="s">
         <v>39</v>
       </c>
       <c r="D8" s="1">
         <v>14</v>
       </c>
       <c r="E8">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="F8" t="s">
         <v>40</v>
@@ -2228,7 +2274,7 @@
         <v>29</v>
       </c>
       <c r="L8">
-        <v>4059218</v>
+        <v>4059219</v>
       </c>
       <c r="M8" t="s">
         <v>41</v>
@@ -2240,7 +2286,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" ht="15.75" spans="1:16">
+    <row r="9" spans="1:16">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>10003</v>
@@ -2255,7 +2301,7 @@
         <v>14</v>
       </c>
       <c r="E9">
-        <v>101500</v>
+        <v>103900</v>
       </c>
       <c r="F9" t="s">
         <v>44</v>
@@ -2276,19 +2322,19 @@
         <v>29</v>
       </c>
       <c r="L9">
-        <v>4059219</v>
+        <v>4059220</v>
       </c>
       <c r="M9" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="N9" t="s">
         <v>34</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
-    <row r="10" ht="15.75" spans="1:16">
+    <row r="10" spans="1:16">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>10004</v>
@@ -2297,16 +2343,16 @@
         <v>4059194</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D10" s="1">
         <v>14</v>
       </c>
       <c r="E10">
-        <v>103100</v>
+        <v>105500</v>
       </c>
       <c r="F10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G10" s="1">
         <v>9</v>
@@ -2327,13 +2373,13 @@
         <v>4059220</v>
       </c>
       <c r="M10" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="N10" t="s">
         <v>34</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2341,4 +2387,208 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A5:P8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <sheetData>
+    <row r="5" ht="15.75" spans="1:16">
+      <c r="A5" s="1">
+        <f t="shared" ref="A5:A8" si="0">1000*10+H5</f>
+        <v>10001</v>
+      </c>
+      <c r="B5" s="1">
+        <v>4059191</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="1">
+        <v>14</v>
+      </c>
+      <c r="E5">
+        <v>102000</v>
+      </c>
+      <c r="F5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="1">
+        <v>9</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>9750</v>
+      </c>
+      <c r="J5">
+        <v>1000</v>
+      </c>
+      <c r="K5" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5">
+        <v>4059217</v>
+      </c>
+      <c r="M5" t="s">
+        <v>51</v>
+      </c>
+      <c r="N5" t="s">
+        <v>34</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" spans="1:16">
+      <c r="A6" s="1">
+        <f t="shared" si="0"/>
+        <v>10002</v>
+      </c>
+      <c r="B6" s="1">
+        <v>4059192</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="1">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>102100</v>
+      </c>
+      <c r="F6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" s="1">
+        <v>9</v>
+      </c>
+      <c r="H6" s="1">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>9800</v>
+      </c>
+      <c r="J6">
+        <v>2000</v>
+      </c>
+      <c r="K6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6">
+        <v>4059218</v>
+      </c>
+      <c r="M6" t="s">
+        <v>55</v>
+      </c>
+      <c r="N6" t="s">
+        <v>34</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" spans="1:16">
+      <c r="A7" s="1">
+        <f t="shared" si="0"/>
+        <v>10003</v>
+      </c>
+      <c r="B7" s="1">
+        <v>4059193</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="1">
+        <v>14</v>
+      </c>
+      <c r="E7">
+        <v>101500</v>
+      </c>
+      <c r="F7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="1">
+        <v>9</v>
+      </c>
+      <c r="H7" s="1">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>9700</v>
+      </c>
+      <c r="J7">
+        <v>2000</v>
+      </c>
+      <c r="K7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7">
+        <v>4059219</v>
+      </c>
+      <c r="M7" t="s">
+        <v>41</v>
+      </c>
+      <c r="N7" t="s">
+        <v>34</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" spans="1:16">
+      <c r="A8" s="1">
+        <f t="shared" si="0"/>
+        <v>10004</v>
+      </c>
+      <c r="B8" s="1">
+        <v>4059194</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="1">
+        <v>14</v>
+      </c>
+      <c r="E8">
+        <v>103100</v>
+      </c>
+      <c r="F8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="1">
+        <v>9</v>
+      </c>
+      <c r="H8" s="1">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>9750</v>
+      </c>
+      <c r="J8">
+        <v>2000</v>
+      </c>
+      <c r="K8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L8">
+        <v>4059220</v>
+      </c>
+      <c r="M8" t="s">
+        <v>37</v>
+      </c>
+      <c r="N8" t="s">
+        <v>34</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/hall/resources/sample/SeasonStart.xlsx
+++ b/hall/resources/sample/SeasonStart.xlsx
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="62">
   <si>
     <t>活动ID</t>
   </si>
@@ -220,16 +220,13 @@
     <t>100_1000</t>
   </si>
   <si>
-    <t>单线玩法</t>
+    <t>拓展转轴</t>
   </si>
   <si>
     <t>进阶赛季</t>
   </si>
   <si>
     <t>蒸汽时代</t>
-  </si>
-  <si>
-    <t>拓展转轴</t>
   </si>
   <si>
     <t>300800_400800</t>
@@ -1974,7 +1971,9 @@
     <col min="7" max="8" width="15.25" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="14.25" customWidth="1"/>
+    <col min="11" max="11" width="14.125" customWidth="1"/>
     <col min="12" max="12" width="15.25" customWidth="1"/>
+    <col min="13" max="13" width="10.75" customWidth="1"/>
     <col min="14" max="14" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2142,7 +2141,7 @@
         <v>29</v>
       </c>
       <c r="L5">
-        <v>4059215</v>
+        <v>4059216</v>
       </c>
       <c r="M5" t="s">
         <v>30</v>
@@ -2184,10 +2183,10 @@
         <v>4059216</v>
       </c>
       <c r="M6" t="s">
+        <v>30</v>
+      </c>
+      <c r="N6" t="s">
         <v>33</v>
-      </c>
-      <c r="N6" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2199,7 +2198,7 @@
         <v>4059191</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" s="1">
         <v>14</v>
@@ -2208,7 +2207,7 @@
         <v>103800</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G7" s="1">
         <v>9</v>
@@ -2229,13 +2228,13 @@
         <v>4059220</v>
       </c>
       <c r="M7" t="s">
+        <v>36</v>
+      </c>
+      <c r="N7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P7" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="N7" t="s">
-        <v>34</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2247,7 +2246,7 @@
         <v>4059192</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8" s="1">
         <v>14</v>
@@ -2256,7 +2255,7 @@
         <v>101700</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G8" s="1">
         <v>9</v>
@@ -2277,13 +2276,13 @@
         <v>4059219</v>
       </c>
       <c r="M8" t="s">
+        <v>40</v>
+      </c>
+      <c r="N8" t="s">
+        <v>33</v>
+      </c>
+      <c r="P8" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="N8" t="s">
-        <v>34</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2295,7 +2294,7 @@
         <v>4059193</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D9" s="1">
         <v>14</v>
@@ -2304,7 +2303,7 @@
         <v>103900</v>
       </c>
       <c r="F9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G9" s="1">
         <v>9</v>
@@ -2325,13 +2324,13 @@
         <v>4059220</v>
       </c>
       <c r="M9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2343,7 +2342,7 @@
         <v>4059194</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D10" s="1">
         <v>14</v>
@@ -2352,7 +2351,7 @@
         <v>105500</v>
       </c>
       <c r="F10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G10" s="1">
         <v>9</v>
@@ -2373,13 +2372,13 @@
         <v>4059220</v>
       </c>
       <c r="M10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2404,7 +2403,7 @@
         <v>4059191</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D5" s="1">
         <v>14</v>
@@ -2413,7 +2412,7 @@
         <v>102000</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G5" s="1">
         <v>9</v>
@@ -2434,13 +2433,13 @@
         <v>4059217</v>
       </c>
       <c r="M5" t="s">
+        <v>50</v>
+      </c>
+      <c r="N5" t="s">
+        <v>33</v>
+      </c>
+      <c r="P5" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="N5" t="s">
-        <v>34</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:16">
@@ -2452,7 +2451,7 @@
         <v>4059192</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D6" s="1">
         <v>14</v>
@@ -2461,7 +2460,7 @@
         <v>102100</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G6" s="1">
         <v>9</v>
@@ -2482,13 +2481,13 @@
         <v>4059218</v>
       </c>
       <c r="M6" t="s">
+        <v>54</v>
+      </c>
+      <c r="N6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P6" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="N6" t="s">
-        <v>34</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:16">
@@ -2500,7 +2499,7 @@
         <v>4059193</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D7" s="1">
         <v>14</v>
@@ -2509,7 +2508,7 @@
         <v>101500</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G7" s="1">
         <v>9</v>
@@ -2530,13 +2529,13 @@
         <v>4059219</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:16">
@@ -2548,7 +2547,7 @@
         <v>4059194</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D8" s="1">
         <v>14</v>
@@ -2557,7 +2556,7 @@
         <v>103100</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G8" s="1">
         <v>9</v>
@@ -2578,13 +2577,13 @@
         <v>4059220</v>
       </c>
       <c r="M8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/SeasonStart.xlsx
+++ b/hall/resources/sample/SeasonStart.xlsx
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="62">
   <si>
     <t>活动ID</t>
   </si>
@@ -229,58 +229,58 @@
     <t>蒸汽时代</t>
   </si>
   <si>
+    <t>恶魔之子赛季</t>
+  </si>
+  <si>
+    <t>恶魔之子</t>
+  </si>
+  <si>
+    <t>中奖线玩法</t>
+  </si>
+  <si>
+    <t>暗影降临/地狱之门/血月之约/魔焰重燃</t>
+  </si>
+  <si>
+    <t>雪国狂欢赛季</t>
+  </si>
+  <si>
+    <t>圣诞狂欢夜</t>
+  </si>
+  <si>
+    <t>中奖消除</t>
+  </si>
+  <si>
+    <t>圣诞颂歌/礼物狂潮/冬日盛宴/北极星之愿/圣诞工厂</t>
+  </si>
+  <si>
+    <t>热血足球赛季</t>
+  </si>
+  <si>
+    <t>热血足球</t>
+  </si>
+  <si>
+    <t>冠军之路/热血杯赛/传奇赛季/绿茵荣耀/点球传奇</t>
+  </si>
+  <si>
+    <t>宝石觉醒赛季</t>
+  </si>
+  <si>
+    <t>伽罗宝石</t>
+  </si>
+  <si>
+    <t>伽罗秘术/伽罗契约/永恒晶石/宝石幻境/魔力宝石季</t>
+  </si>
+  <si>
+    <t>神域对决赛季</t>
+  </si>
+  <si>
+    <t>宙斯VS哈迪斯</t>
+  </si>
+  <si>
+    <t>扩展百搭</t>
+  </si>
+  <si>
     <t>300800_400800</t>
-  </si>
-  <si>
-    <t>恶魔之子赛季</t>
-  </si>
-  <si>
-    <t>恶魔之子</t>
-  </si>
-  <si>
-    <t>中奖线玩法</t>
-  </si>
-  <si>
-    <t>暗影降临/地狱之门/血月之约/魔焰重燃</t>
-  </si>
-  <si>
-    <t>雪国狂欢赛季</t>
-  </si>
-  <si>
-    <t>圣诞狂欢夜</t>
-  </si>
-  <si>
-    <t>中奖消除</t>
-  </si>
-  <si>
-    <t>圣诞颂歌/礼物狂潮/冬日盛宴/北极星之愿/圣诞工厂</t>
-  </si>
-  <si>
-    <t>愤怒风暴赛季</t>
-  </si>
-  <si>
-    <t>愤怒的小鸟</t>
-  </si>
-  <si>
-    <t>暴走小鸟季/破壳时刻/复仇纪元/蛋之守护/猪猪末日</t>
-  </si>
-  <si>
-    <t>宝石觉醒赛季</t>
-  </si>
-  <si>
-    <t>伽罗宝石</t>
-  </si>
-  <si>
-    <t>伽罗秘术/伽罗契约/永恒晶石/宝石幻境/魔力宝石季</t>
-  </si>
-  <si>
-    <t>神域对决赛季</t>
-  </si>
-  <si>
-    <t>宙斯VS哈迪斯</t>
-  </si>
-  <si>
-    <t>扩展百搭</t>
   </si>
   <si>
     <r>
@@ -961,12 +961,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2119,7 +2119,7 @@
         <v>27</v>
       </c>
       <c r="D5" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5" s="1">
         <v>101400</v>
@@ -2158,7 +2158,7 @@
         <v>31</v>
       </c>
       <c r="D6" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>102300</v>
@@ -2184,9 +2184,6 @@
       </c>
       <c r="M6" t="s">
         <v>30</v>
-      </c>
-      <c r="N6" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2198,7 +2195,7 @@
         <v>4059191</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" s="1">
         <v>14</v>
@@ -2207,7 +2204,7 @@
         <v>103800</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G7" s="1">
         <v>9</v>
@@ -2228,13 +2225,11 @@
         <v>4059220</v>
       </c>
       <c r="M7" t="s">
+        <v>35</v>
+      </c>
+      <c r="N7"/>
+      <c r="P7" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="N7" t="s">
-        <v>33</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2246,7 +2241,7 @@
         <v>4059192</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D8" s="1">
         <v>14</v>
@@ -2255,7 +2250,7 @@
         <v>101700</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G8" s="1">
         <v>9</v>
@@ -2276,13 +2271,11 @@
         <v>4059219</v>
       </c>
       <c r="M8" t="s">
+        <v>39</v>
+      </c>
+      <c r="N8"/>
+      <c r="P8" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="N8" t="s">
-        <v>33</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2294,16 +2287,16 @@
         <v>4059193</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" s="1">
         <v>14</v>
       </c>
       <c r="E9">
-        <v>103900</v>
+        <v>101600</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G9" s="1">
         <v>9</v>
@@ -2321,16 +2314,14 @@
         <v>29</v>
       </c>
       <c r="L9">
-        <v>4059220</v>
+        <v>4059219</v>
       </c>
       <c r="M9" t="s">
-        <v>36</v>
-      </c>
-      <c r="N9" t="s">
-        <v>33</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="N9"/>
       <c r="P9" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2342,7 +2333,7 @@
         <v>4059194</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" s="1">
         <v>14</v>
@@ -2351,7 +2342,7 @@
         <v>105500</v>
       </c>
       <c r="F10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G10" s="1">
         <v>9</v>
@@ -2372,13 +2363,11 @@
         <v>4059220</v>
       </c>
       <c r="M10" t="s">
-        <v>36</v>
-      </c>
-      <c r="N10" t="s">
-        <v>33</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="N10"/>
       <c r="P10" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -2403,7 +2392,7 @@
         <v>4059191</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D5" s="1">
         <v>14</v>
@@ -2412,7 +2401,7 @@
         <v>102000</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G5" s="1">
         <v>9</v>
@@ -2433,10 +2422,10 @@
         <v>4059217</v>
       </c>
       <c r="M5" t="s">
+        <v>49</v>
+      </c>
+      <c r="N5" t="s">
         <v>50</v>
-      </c>
-      <c r="N5" t="s">
-        <v>33</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>51</v>
@@ -2484,7 +2473,7 @@
         <v>54</v>
       </c>
       <c r="N6" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>55</v>
@@ -2529,10 +2518,10 @@
         <v>4059219</v>
       </c>
       <c r="M7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N7" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>58</v>
@@ -2577,10 +2566,10 @@
         <v>4059220</v>
       </c>
       <c r="M8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N8" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>61</v>

--- a/hall/resources/sample/SeasonStart.xlsx
+++ b/hall/resources/sample/SeasonStart.xlsx
@@ -2227,7 +2227,9 @@
       <c r="M7" t="s">
         <v>35</v>
       </c>
-      <c r="N7"/>
+      <c r="N7">
+        <v>300800</v>
+      </c>
       <c r="P7" s="2" t="s">
         <v>36</v>
       </c>
@@ -2273,7 +2275,6 @@
       <c r="M8" t="s">
         <v>39</v>
       </c>
-      <c r="N8"/>
       <c r="P8" s="2" t="s">
         <v>40</v>
       </c>
@@ -2319,7 +2320,6 @@
       <c r="M9" t="s">
         <v>39</v>
       </c>
-      <c r="N9"/>
       <c r="P9" s="2" t="s">
         <v>43</v>
       </c>
@@ -2365,7 +2365,6 @@
       <c r="M10" t="s">
         <v>35</v>
       </c>
-      <c r="N10"/>
       <c r="P10" s="2" t="s">
         <v>46</v>
       </c>

--- a/hall/resources/sample/SeasonStart.xlsx
+++ b/hall/resources/sample/SeasonStart.xlsx
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="64">
   <si>
     <t>活动ID</t>
   </si>
@@ -169,6 +169,9 @@
     <t>开启的小游戏</t>
   </si>
   <si>
+    <t>新加入赛季送赛季币</t>
+  </si>
+  <si>
     <t>赛季名称备选</t>
   </si>
   <si>
@@ -209,6 +212,9 @@
   </si>
   <si>
     <t>Openminigame</t>
+  </si>
+  <si>
+    <t>NewJoinSeasonCoin</t>
   </si>
   <si>
     <t>新手赛季</t>
@@ -1975,6 +1981,7 @@
     <col min="12" max="12" width="15.25" customWidth="1"/>
     <col min="13" max="13" width="10.75" customWidth="1"/>
     <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="15" width="20.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2020,82 +2027,91 @@
       <c r="N1" t="s">
         <v>12</v>
       </c>
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
       <c r="P1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" t="s">
         <v>15</v>
       </c>
-      <c r="L2" t="s">
-        <v>14</v>
-      </c>
       <c r="N2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="O3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2116,7 +2132,7 @@
         <v>4059002</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -2125,7 +2141,7 @@
         <v>101400</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G5" s="1">
         <v>3</v>
@@ -2138,13 +2154,16 @@
         <v>1000</v>
       </c>
       <c r="K5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L5">
         <v>4059216</v>
       </c>
       <c r="M5" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="O5">
+        <v>1000</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2155,7 +2174,7 @@
         <v>4059094</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
@@ -2164,7 +2183,7 @@
         <v>102300</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G6" s="1">
         <v>6</v>
@@ -2177,13 +2196,16 @@
         <v>3300</v>
       </c>
       <c r="K6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L6">
         <v>4059216</v>
       </c>
       <c r="M6" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="O6">
+        <v>2000</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2195,7 +2217,7 @@
         <v>4059191</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D7" s="1">
         <v>14</v>
@@ -2204,7 +2226,7 @@
         <v>103800</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G7" s="1">
         <v>9</v>
@@ -2219,19 +2241,22 @@
         <v>1000</v>
       </c>
       <c r="K7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L7">
         <v>4059220</v>
       </c>
       <c r="M7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N7">
         <v>300800</v>
       </c>
+      <c r="O7">
+        <v>12000</v>
+      </c>
       <c r="P7" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2243,7 +2268,7 @@
         <v>4059192</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D8" s="1">
         <v>14</v>
@@ -2252,7 +2277,7 @@
         <v>101700</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G8" s="1">
         <v>9</v>
@@ -2267,16 +2292,19 @@
         <v>2000</v>
       </c>
       <c r="K8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L8">
         <v>4059219</v>
       </c>
       <c r="M8" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="O8">
+        <v>12000</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2288,7 +2316,7 @@
         <v>4059193</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D9" s="1">
         <v>14</v>
@@ -2297,7 +2325,7 @@
         <v>101600</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G9" s="1">
         <v>9</v>
@@ -2312,16 +2340,19 @@
         <v>2000</v>
       </c>
       <c r="K9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L9">
         <v>4059219</v>
       </c>
       <c r="M9" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="O9">
+        <v>12000</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2333,7 +2364,7 @@
         <v>4059194</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D10" s="1">
         <v>14</v>
@@ -2342,7 +2373,7 @@
         <v>105500</v>
       </c>
       <c r="F10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G10" s="1">
         <v>9</v>
@@ -2357,16 +2388,19 @@
         <v>2000</v>
       </c>
       <c r="K10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L10">
         <v>4059220</v>
       </c>
       <c r="M10" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="O10">
+        <v>12000</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2391,7 +2425,7 @@
         <v>4059191</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D5" s="1">
         <v>14</v>
@@ -2400,7 +2434,7 @@
         <v>102000</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G5" s="1">
         <v>9</v>
@@ -2415,19 +2449,19 @@
         <v>1000</v>
       </c>
       <c r="K5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L5">
         <v>4059217</v>
       </c>
       <c r="M5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:16">
@@ -2439,7 +2473,7 @@
         <v>4059192</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D6" s="1">
         <v>14</v>
@@ -2448,7 +2482,7 @@
         <v>102100</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G6" s="1">
         <v>9</v>
@@ -2463,19 +2497,19 @@
         <v>2000</v>
       </c>
       <c r="K6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L6">
         <v>4059218</v>
       </c>
       <c r="M6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:16">
@@ -2487,7 +2521,7 @@
         <v>4059193</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D7" s="1">
         <v>14</v>
@@ -2496,7 +2530,7 @@
         <v>101500</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G7" s="1">
         <v>9</v>
@@ -2511,19 +2545,19 @@
         <v>2000</v>
       </c>
       <c r="K7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L7">
         <v>4059219</v>
       </c>
       <c r="M7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:16">
@@ -2535,7 +2569,7 @@
         <v>4059194</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D8" s="1">
         <v>14</v>
@@ -2544,7 +2578,7 @@
         <v>103100</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G8" s="1">
         <v>9</v>
@@ -2559,19 +2593,19 @@
         <v>2000</v>
       </c>
       <c r="K8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L8">
         <v>4059220</v>
       </c>
       <c r="M8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/SeasonStart.xlsx
+++ b/hall/resources/sample/SeasonStart.xlsx
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="65">
   <si>
     <t>活动ID</t>
   </si>
@@ -223,64 +223,67 @@
     <t>埃及艳后</t>
   </si>
   <si>
+    <t>200_1000</t>
+  </si>
+  <si>
+    <t>拓展转轴</t>
+  </si>
+  <si>
+    <t>进阶赛季</t>
+  </si>
+  <si>
+    <t>蒸汽时代</t>
+  </si>
+  <si>
+    <t>恶魔之子赛季</t>
+  </si>
+  <si>
+    <t>恶魔之子</t>
+  </si>
+  <si>
+    <t>中奖线玩法</t>
+  </si>
+  <si>
+    <t>暗影降临/地狱之门/血月之约/魔焰重燃</t>
+  </si>
+  <si>
+    <t>雪国狂欢赛季</t>
+  </si>
+  <si>
+    <t>圣诞狂欢夜</t>
+  </si>
+  <si>
+    <t>中奖消除</t>
+  </si>
+  <si>
+    <t>圣诞颂歌/礼物狂潮/冬日盛宴/北极星之愿/圣诞工厂</t>
+  </si>
+  <si>
+    <t>热血足球赛季</t>
+  </si>
+  <si>
+    <t>热血足球</t>
+  </si>
+  <si>
+    <t>冠军之路/热血杯赛/传奇赛季/绿茵荣耀/点球传奇</t>
+  </si>
+  <si>
+    <t>宝石觉醒赛季</t>
+  </si>
+  <si>
+    <t>伽罗宝石</t>
+  </si>
+  <si>
+    <t>伽罗秘术/伽罗契约/永恒晶石/宝石幻境/魔力宝石季</t>
+  </si>
+  <si>
+    <t>神域对决赛季</t>
+  </si>
+  <si>
+    <t>宙斯VS哈迪斯</t>
+  </si>
+  <si>
     <t>100_1000</t>
-  </si>
-  <si>
-    <t>拓展转轴</t>
-  </si>
-  <si>
-    <t>进阶赛季</t>
-  </si>
-  <si>
-    <t>蒸汽时代</t>
-  </si>
-  <si>
-    <t>恶魔之子赛季</t>
-  </si>
-  <si>
-    <t>恶魔之子</t>
-  </si>
-  <si>
-    <t>中奖线玩法</t>
-  </si>
-  <si>
-    <t>暗影降临/地狱之门/血月之约/魔焰重燃</t>
-  </si>
-  <si>
-    <t>雪国狂欢赛季</t>
-  </si>
-  <si>
-    <t>圣诞狂欢夜</t>
-  </si>
-  <si>
-    <t>中奖消除</t>
-  </si>
-  <si>
-    <t>圣诞颂歌/礼物狂潮/冬日盛宴/北极星之愿/圣诞工厂</t>
-  </si>
-  <si>
-    <t>热血足球赛季</t>
-  </si>
-  <si>
-    <t>热血足球</t>
-  </si>
-  <si>
-    <t>冠军之路/热血杯赛/传奇赛季/绿茵荣耀/点球传奇</t>
-  </si>
-  <si>
-    <t>宝石觉醒赛季</t>
-  </si>
-  <si>
-    <t>伽罗宝石</t>
-  </si>
-  <si>
-    <t>伽罗秘术/伽罗契约/永恒晶石/宝石幻境/魔力宝石季</t>
-  </si>
-  <si>
-    <t>神域对决赛季</t>
-  </si>
-  <si>
-    <t>宙斯VS哈迪斯</t>
   </si>
   <si>
     <t>扩展百搭</t>
@@ -2449,19 +2452,19 @@
         <v>1000</v>
       </c>
       <c r="K5" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="L5">
         <v>4059217</v>
       </c>
       <c r="M5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:16">
@@ -2473,7 +2476,7 @@
         <v>4059192</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D6" s="1">
         <v>14</v>
@@ -2482,7 +2485,7 @@
         <v>102100</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G6" s="1">
         <v>9</v>
@@ -2497,19 +2500,19 @@
         <v>2000</v>
       </c>
       <c r="K6" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="L6">
         <v>4059218</v>
       </c>
       <c r="M6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:16">
@@ -2521,7 +2524,7 @@
         <v>4059193</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D7" s="1">
         <v>14</v>
@@ -2530,7 +2533,7 @@
         <v>101500</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G7" s="1">
         <v>9</v>
@@ -2545,7 +2548,7 @@
         <v>2000</v>
       </c>
       <c r="K7" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="L7">
         <v>4059219</v>
@@ -2554,10 +2557,10 @@
         <v>41</v>
       </c>
       <c r="N7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:16">
@@ -2569,7 +2572,7 @@
         <v>4059194</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D8" s="1">
         <v>14</v>
@@ -2578,7 +2581,7 @@
         <v>103100</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G8" s="1">
         <v>9</v>
@@ -2593,7 +2596,7 @@
         <v>2000</v>
       </c>
       <c r="K8" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="L8">
         <v>4059220</v>
@@ -2602,10 +2605,10 @@
         <v>37</v>
       </c>
       <c r="N8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/SeasonStart.xlsx
+++ b/hall/resources/sample/SeasonStart.xlsx
@@ -223,7 +223,7 @@
     <t>埃及艳后</t>
   </si>
   <si>
-    <t>200_1000</t>
+    <t>200_3600</t>
   </si>
   <si>
     <t>拓展转轴</t>

--- a/hall/resources/sample/SeasonStart.xlsx
+++ b/hall/resources/sample/SeasonStart.xlsx
@@ -2303,6 +2303,9 @@
       <c r="M8" t="s">
         <v>41</v>
       </c>
+      <c r="N8">
+        <v>300800</v>
+      </c>
       <c r="O8">
         <v>12000</v>
       </c>
@@ -2351,6 +2354,9 @@
       <c r="M9" t="s">
         <v>41</v>
       </c>
+      <c r="N9">
+        <v>300800</v>
+      </c>
       <c r="O9">
         <v>12000</v>
       </c>
@@ -2398,6 +2404,9 @@
       </c>
       <c r="M10" t="s">
         <v>37</v>
+      </c>
+      <c r="N10">
+        <v>300800</v>
       </c>
       <c r="O10">
         <v>12000</v>

--- a/hall/resources/sample/SeasonStart.xlsx
+++ b/hall/resources/sample/SeasonStart.xlsx
@@ -1,14 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SeasonStart" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -127,8 +133,108 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1.万比分，前端显示为百分比；
+2.此值不为对应游戏实际的RTP，只是用于前端显示；</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+此值用于前端显示</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1.用于前端显示；
+2.此值的上限根据赛季玩法的宝石（下注）进行调整，宝石的上限提升后，此值的上限也进行提升，要相互对应</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1.显示多语言，用于前端显示</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="67">
   <si>
     <t>活动ID</t>
   </si>
@@ -172,6 +278,9 @@
     <t>新加入赛季送赛季币</t>
   </si>
   <si>
+    <t>赛季通行证</t>
+  </si>
+  <si>
     <t>赛季名称备选</t>
   </si>
   <si>
@@ -244,37 +353,40 @@
     <t>中奖线玩法</t>
   </si>
   <si>
+    <t>1002_1003_1004</t>
+  </si>
+  <si>
     <t>暗影降临/地狱之门/血月之约/魔焰重燃</t>
   </si>
   <si>
     <t>雪国狂欢赛季</t>
   </si>
   <si>
+    <t>中奖消除</t>
+  </si>
+  <si>
+    <t>圣诞颂歌/礼物狂潮/冬日盛宴/北极星之愿/圣诞工厂</t>
+  </si>
+  <si>
+    <t>热血足球赛季</t>
+  </si>
+  <si>
+    <t>冠军之路/热血杯赛/传奇赛季/绿茵荣耀/点球传奇</t>
+  </si>
+  <si>
+    <t>宝石觉醒赛季</t>
+  </si>
+  <si>
+    <t>伽罗秘术/伽罗契约/永恒晶石/宝石幻境/魔力宝石季</t>
+  </si>
+  <si>
     <t>圣诞狂欢夜</t>
   </si>
   <si>
-    <t>中奖消除</t>
-  </si>
-  <si>
-    <t>圣诞颂歌/礼物狂潮/冬日盛宴/北极星之愿/圣诞工厂</t>
-  </si>
-  <si>
-    <t>热血足球赛季</t>
-  </si>
-  <si>
     <t>热血足球</t>
   </si>
   <si>
-    <t>冠军之路/热血杯赛/传奇赛季/绿茵荣耀/点球传奇</t>
-  </si>
-  <si>
-    <t>宝石觉醒赛季</t>
-  </si>
-  <si>
     <t>伽罗宝石</t>
-  </si>
-  <si>
-    <t>伽罗秘术/伽罗契约/永恒晶石/宝石幻境/魔力宝石季</t>
   </si>
   <si>
     <t>神域对决赛季</t>
@@ -1969,6 +2081,484 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="11.375" customWidth="1"/>
+    <col min="4" max="4" width="15.875" customWidth="1"/>
+    <col min="5" max="5" width="13.625" customWidth="1"/>
+    <col min="6" max="6" width="12.625" customWidth="1"/>
+    <col min="7" max="8" width="15.25" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="14.25" customWidth="1"/>
+    <col min="11" max="11" width="14.125" customWidth="1"/>
+    <col min="12" max="12" width="15.25" customWidth="1"/>
+    <col min="13" max="13" width="10.75" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="15" width="20.25" customWidth="1"/>
+    <col min="16" max="16" width="11.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" s="1">
+        <v>1001</v>
+      </c>
+      <c r="B5" s="1">
+        <v>4059002</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1">
+        <v>101400</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="1">
+        <v>3</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="I5">
+        <v>9650</v>
+      </c>
+      <c r="J5">
+        <v>1000</v>
+      </c>
+      <c r="K5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5">
+        <v>4059216</v>
+      </c>
+      <c r="M5" t="s">
+        <v>33</v>
+      </c>
+      <c r="O5">
+        <v>1000</v>
+      </c>
+      <c r="P5">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" s="1">
+        <v>1002</v>
+      </c>
+      <c r="B6" s="1">
+        <v>4059094</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>102300</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="1">
+        <v>6</v>
+      </c>
+      <c r="H6" s="1"/>
+      <c r="I6">
+        <v>9700</v>
+      </c>
+      <c r="J6">
+        <v>3300</v>
+      </c>
+      <c r="K6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6">
+        <v>4059216</v>
+      </c>
+      <c r="M6" t="s">
+        <v>33</v>
+      </c>
+      <c r="O6">
+        <v>2000</v>
+      </c>
+      <c r="P6">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="1">
+        <f>1000*10+H7</f>
+        <v>10001</v>
+      </c>
+      <c r="B7" s="1">
+        <v>4059191</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="1">
+        <v>14</v>
+      </c>
+      <c r="E7">
+        <v>103800</v>
+      </c>
+      <c r="F7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="1">
+        <v>9</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>9750</v>
+      </c>
+      <c r="J7">
+        <v>1000</v>
+      </c>
+      <c r="K7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7">
+        <v>4059220</v>
+      </c>
+      <c r="M7" t="s">
+        <v>38</v>
+      </c>
+      <c r="N7">
+        <v>300800</v>
+      </c>
+      <c r="O7">
+        <v>12000</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" s="1">
+        <f t="shared" ref="A7:A10" si="0">1000*10+H8</f>
+        <v>10002</v>
+      </c>
+      <c r="B8" s="1">
+        <v>4059191</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="1">
+        <v>14</v>
+      </c>
+      <c r="E8">
+        <v>103800</v>
+      </c>
+      <c r="F8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="1">
+        <v>9</v>
+      </c>
+      <c r="H8" s="1">
+        <v>2</v>
+      </c>
+      <c r="I8">
+        <v>9800</v>
+      </c>
+      <c r="J8">
+        <v>2000</v>
+      </c>
+      <c r="K8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8">
+        <v>4059219</v>
+      </c>
+      <c r="M8" t="s">
+        <v>42</v>
+      </c>
+      <c r="N8">
+        <v>300800</v>
+      </c>
+      <c r="O8">
+        <v>12000</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="1">
+        <f t="shared" si="0"/>
+        <v>10003</v>
+      </c>
+      <c r="B9" s="1">
+        <v>4059191</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="1">
+        <v>14</v>
+      </c>
+      <c r="E9">
+        <v>103800</v>
+      </c>
+      <c r="F9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="1">
+        <v>9</v>
+      </c>
+      <c r="H9" s="1">
+        <v>3</v>
+      </c>
+      <c r="I9">
+        <v>9700</v>
+      </c>
+      <c r="J9">
+        <v>2000</v>
+      </c>
+      <c r="K9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9">
+        <v>4059219</v>
+      </c>
+      <c r="M9" t="s">
+        <v>42</v>
+      </c>
+      <c r="N9">
+        <v>300800</v>
+      </c>
+      <c r="O9">
+        <v>12000</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" s="1">
+        <f t="shared" si="0"/>
+        <v>10004</v>
+      </c>
+      <c r="B10" s="1">
+        <v>4059191</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="1">
+        <v>14</v>
+      </c>
+      <c r="E10">
+        <v>103800</v>
+      </c>
+      <c r="F10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="1">
+        <v>9</v>
+      </c>
+      <c r="H10" s="1">
+        <v>4</v>
+      </c>
+      <c r="I10">
+        <v>9750</v>
+      </c>
+      <c r="J10">
+        <v>2000</v>
+      </c>
+      <c r="K10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10">
+        <v>4059220</v>
+      </c>
+      <c r="M10" t="s">
+        <v>38</v>
+      </c>
+      <c r="N10">
+        <v>300800</v>
+      </c>
+      <c r="O10">
+        <v>12000</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:P10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
@@ -2034,87 +2624,87 @@
         <v>13</v>
       </c>
       <c r="P1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" t="s">
         <v>16</v>
       </c>
-      <c r="L2" t="s">
-        <v>15</v>
-      </c>
       <c r="N2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2" t="s">
         <v>16</v>
-      </c>
-      <c r="O2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2135,7 +2725,7 @@
         <v>4059002</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -2144,7 +2734,7 @@
         <v>101400</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5" s="1">
         <v>3</v>
@@ -2157,13 +2747,13 @@
         <v>1000</v>
       </c>
       <c r="K5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L5">
         <v>4059216</v>
       </c>
       <c r="M5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O5">
         <v>1000</v>
@@ -2177,7 +2767,7 @@
         <v>4059094</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
@@ -2186,7 +2776,7 @@
         <v>102300</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G6" s="1">
         <v>6</v>
@@ -2199,13 +2789,13 @@
         <v>3300</v>
       </c>
       <c r="K6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L6">
         <v>4059216</v>
       </c>
       <c r="M6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O6">
         <v>2000</v>
@@ -2213,14 +2803,14 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1">
-        <f>1000*10+H7</f>
+        <f t="shared" ref="A7:A10" si="0">1000*10+H7</f>
         <v>10001</v>
       </c>
       <c r="B7" s="1">
         <v>4059191</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" s="1">
         <v>14</v>
@@ -2229,7 +2819,7 @@
         <v>103800</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7" s="1">
         <v>9</v>
@@ -2244,13 +2834,13 @@
         <v>1000</v>
       </c>
       <c r="K7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L7">
         <v>4059220</v>
       </c>
       <c r="M7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N7">
         <v>300800</v>
@@ -2259,19 +2849,19 @@
         <v>12000</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1">
-        <f t="shared" ref="A7:A10" si="0">1000*10+H8</f>
+        <f t="shared" si="0"/>
         <v>10002</v>
       </c>
       <c r="B8" s="1">
         <v>4059192</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D8" s="1">
         <v>14</v>
@@ -2280,7 +2870,7 @@
         <v>101700</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G8" s="1">
         <v>9</v>
@@ -2295,13 +2885,13 @@
         <v>2000</v>
       </c>
       <c r="K8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L8">
         <v>4059219</v>
       </c>
       <c r="M8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N8">
         <v>300800</v>
@@ -2310,7 +2900,7 @@
         <v>12000</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2322,7 +2912,7 @@
         <v>4059193</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" s="1">
         <v>14</v>
@@ -2331,7 +2921,7 @@
         <v>101600</v>
       </c>
       <c r="F9" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G9" s="1">
         <v>9</v>
@@ -2346,13 +2936,13 @@
         <v>2000</v>
       </c>
       <c r="K9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L9">
         <v>4059219</v>
       </c>
       <c r="M9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N9">
         <v>300800</v>
@@ -2382,7 +2972,7 @@
         <v>105500</v>
       </c>
       <c r="F10" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G10" s="1">
         <v>9</v>
@@ -2397,13 +2987,13 @@
         <v>2000</v>
       </c>
       <c r="K10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L10">
         <v>4059220</v>
       </c>
       <c r="M10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N10">
         <v>300800</v>
@@ -2412,7 +3002,7 @@
         <v>12000</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2422,7 +3012,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A5:P8"/>
@@ -2437,7 +3027,7 @@
         <v>4059191</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D5" s="1">
         <v>14</v>
@@ -2446,7 +3036,7 @@
         <v>102000</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G5" s="1">
         <v>9</v>
@@ -2461,19 +3051,19 @@
         <v>1000</v>
       </c>
       <c r="K5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L5">
         <v>4059217</v>
       </c>
       <c r="M5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:16">
@@ -2485,7 +3075,7 @@
         <v>4059192</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D6" s="1">
         <v>14</v>
@@ -2494,7 +3084,7 @@
         <v>102100</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G6" s="1">
         <v>9</v>
@@ -2509,19 +3099,19 @@
         <v>2000</v>
       </c>
       <c r="K6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L6">
         <v>4059218</v>
       </c>
       <c r="M6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:16">
@@ -2533,7 +3123,7 @@
         <v>4059193</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D7" s="1">
         <v>14</v>
@@ -2542,7 +3132,7 @@
         <v>101500</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G7" s="1">
         <v>9</v>
@@ -2557,19 +3147,19 @@
         <v>2000</v>
       </c>
       <c r="K7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L7">
         <v>4059219</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:16">
@@ -2581,7 +3171,7 @@
         <v>4059194</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D8" s="1">
         <v>14</v>
@@ -2590,7 +3180,7 @@
         <v>103100</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G8" s="1">
         <v>9</v>
@@ -2605,19 +3195,19 @@
         <v>2000</v>
       </c>
       <c r="K8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L8">
         <v>4059220</v>
       </c>
       <c r="M8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/SeasonStart.xlsx
+++ b/hall/resources/sample/SeasonStart.xlsx
@@ -234,7 +234,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="67">
   <si>
     <t>活动ID</t>
   </si>
@@ -353,6 +353,9 @@
     <t>中奖线玩法</t>
   </si>
   <si>
+    <t>300800_400800</t>
+  </si>
+  <si>
     <t>1002_1003_1004</t>
   </si>
   <si>
@@ -399,9 +402,6 @@
   </si>
   <si>
     <t>扩展百搭</t>
-  </si>
-  <si>
-    <t>300800_400800</t>
   </si>
   <si>
     <r>
@@ -2374,17 +2374,17 @@
       <c r="M7" t="s">
         <v>38</v>
       </c>
-      <c r="N7">
-        <v>300800</v>
+      <c r="N7" t="s">
+        <v>39</v>
       </c>
       <c r="O7">
         <v>12000</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -2396,7 +2396,7 @@
         <v>4059191</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" s="1">
         <v>14</v>
@@ -2426,19 +2426,19 @@
         <v>4059219</v>
       </c>
       <c r="M8" t="s">
-        <v>42</v>
-      </c>
-      <c r="N8">
-        <v>300800</v>
+        <v>43</v>
+      </c>
+      <c r="N8" t="s">
+        <v>39</v>
       </c>
       <c r="O8">
         <v>12000</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -2450,7 +2450,7 @@
         <v>4059191</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9" s="1">
         <v>14</v>
@@ -2480,19 +2480,19 @@
         <v>4059219</v>
       </c>
       <c r="M9" t="s">
-        <v>42</v>
-      </c>
-      <c r="N9">
-        <v>300800</v>
+        <v>43</v>
+      </c>
+      <c r="N9" t="s">
+        <v>39</v>
       </c>
       <c r="O9">
         <v>12000</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -2504,7 +2504,7 @@
         <v>4059191</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" s="1">
         <v>14</v>
@@ -2536,17 +2536,17 @@
       <c r="M10" t="s">
         <v>38</v>
       </c>
-      <c r="N10">
-        <v>300800</v>
+      <c r="N10" t="s">
+        <v>39</v>
       </c>
       <c r="O10">
         <v>12000</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2849,7 +2849,7 @@
         <v>12000</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2861,7 +2861,7 @@
         <v>4059192</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" s="1">
         <v>14</v>
@@ -2870,7 +2870,7 @@
         <v>101700</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G8" s="1">
         <v>9</v>
@@ -2891,7 +2891,7 @@
         <v>4059219</v>
       </c>
       <c r="M8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N8">
         <v>300800</v>
@@ -2900,7 +2900,7 @@
         <v>12000</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2912,7 +2912,7 @@
         <v>4059193</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9" s="1">
         <v>14</v>
@@ -2921,7 +2921,7 @@
         <v>101600</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G9" s="1">
         <v>9</v>
@@ -2942,7 +2942,7 @@
         <v>4059219</v>
       </c>
       <c r="M9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N9">
         <v>300800</v>
@@ -2951,7 +2951,7 @@
         <v>12000</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2963,7 +2963,7 @@
         <v>4059194</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" s="1">
         <v>14</v>
@@ -2972,7 +2972,7 @@
         <v>105500</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G10" s="1">
         <v>9</v>
@@ -3002,7 +3002,7 @@
         <v>12000</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -3027,7 +3027,7 @@
         <v>4059191</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5" s="1">
         <v>14</v>
@@ -3036,7 +3036,7 @@
         <v>102000</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G5" s="1">
         <v>9</v>
@@ -3051,16 +3051,16 @@
         <v>1000</v>
       </c>
       <c r="K5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L5">
         <v>4059217</v>
       </c>
       <c r="M5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N5" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>56</v>
@@ -3099,7 +3099,7 @@
         <v>2000</v>
       </c>
       <c r="K6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L6">
         <v>4059218</v>
@@ -3108,7 +3108,7 @@
         <v>59</v>
       </c>
       <c r="N6" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>60</v>
@@ -3147,16 +3147,16 @@
         <v>2000</v>
       </c>
       <c r="K7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L7">
         <v>4059219</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>63</v>
@@ -3195,7 +3195,7 @@
         <v>2000</v>
       </c>
       <c r="K8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L8">
         <v>4059220</v>
@@ -3204,7 +3204,7 @@
         <v>38</v>
       </c>
       <c r="N8" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>66</v>

--- a/hall/resources/sample/SeasonStart.xlsx
+++ b/hall/resources/sample/SeasonStart.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SeasonStart" sheetId="1" r:id="rId1"/>
@@ -234,7 +234,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="68">
   <si>
     <t>活动ID</t>
   </si>
@@ -324,6 +324,9 @@
   </si>
   <si>
     <t>NewJoinSeasonCoin</t>
+  </si>
+  <si>
+    <t>SeasonPass</t>
   </si>
   <si>
     <t>新手赛季</t>
@@ -2192,6 +2195,9 @@
       <c r="O2" t="s">
         <v>16</v>
       </c>
+      <c r="P2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="1" t="s">
@@ -2231,6 +2237,9 @@
       </c>
       <c r="O3" t="s">
         <v>29</v>
+      </c>
+      <c r="P3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -2251,7 +2260,7 @@
         <v>4059002</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -2260,7 +2269,7 @@
         <v>101400</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5" s="1">
         <v>3</v>
@@ -2273,13 +2282,13 @@
         <v>1000</v>
       </c>
       <c r="K5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L5">
         <v>4059216</v>
       </c>
       <c r="M5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O5">
         <v>1000</v>
@@ -2296,7 +2305,7 @@
         <v>4059094</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
@@ -2305,7 +2314,7 @@
         <v>102300</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6" s="1">
         <v>6</v>
@@ -2318,13 +2327,13 @@
         <v>3300</v>
       </c>
       <c r="K6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L6">
         <v>4059216</v>
       </c>
       <c r="M6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O6">
         <v>2000</v>
@@ -2342,7 +2351,7 @@
         <v>4059191</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" s="1">
         <v>14</v>
@@ -2351,7 +2360,7 @@
         <v>103800</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G7" s="1">
         <v>9</v>
@@ -2366,25 +2375,25 @@
         <v>1000</v>
       </c>
       <c r="K7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L7">
         <v>4059220</v>
       </c>
       <c r="M7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O7">
         <v>12000</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -2396,7 +2405,7 @@
         <v>4059191</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D8" s="1">
         <v>14</v>
@@ -2405,7 +2414,7 @@
         <v>103800</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G8" s="1">
         <v>9</v>
@@ -2420,25 +2429,25 @@
         <v>2000</v>
       </c>
       <c r="K8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L8">
         <v>4059219</v>
       </c>
       <c r="M8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O8">
         <v>12000</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -2450,7 +2459,7 @@
         <v>4059191</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" s="1">
         <v>14</v>
@@ -2459,7 +2468,7 @@
         <v>103800</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G9" s="1">
         <v>9</v>
@@ -2474,25 +2483,25 @@
         <v>2000</v>
       </c>
       <c r="K9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L9">
         <v>4059219</v>
       </c>
       <c r="M9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O9">
         <v>12000</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -2504,7 +2513,7 @@
         <v>4059191</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D10" s="1">
         <v>14</v>
@@ -2513,7 +2522,7 @@
         <v>103800</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G10" s="1">
         <v>9</v>
@@ -2528,25 +2537,25 @@
         <v>2000</v>
       </c>
       <c r="K10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L10">
         <v>4059220</v>
       </c>
       <c r="M10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O10">
         <v>12000</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2725,7 +2734,7 @@
         <v>4059002</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -2734,7 +2743,7 @@
         <v>101400</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5" s="1">
         <v>3</v>
@@ -2747,13 +2756,13 @@
         <v>1000</v>
       </c>
       <c r="K5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L5">
         <v>4059216</v>
       </c>
       <c r="M5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O5">
         <v>1000</v>
@@ -2767,7 +2776,7 @@
         <v>4059094</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
@@ -2776,7 +2785,7 @@
         <v>102300</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6" s="1">
         <v>6</v>
@@ -2789,13 +2798,13 @@
         <v>3300</v>
       </c>
       <c r="K6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L6">
         <v>4059216</v>
       </c>
       <c r="M6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O6">
         <v>2000</v>
@@ -2810,7 +2819,7 @@
         <v>4059191</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" s="1">
         <v>14</v>
@@ -2819,7 +2828,7 @@
         <v>103800</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G7" s="1">
         <v>9</v>
@@ -2834,13 +2843,13 @@
         <v>1000</v>
       </c>
       <c r="K7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L7">
         <v>4059220</v>
       </c>
       <c r="M7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N7">
         <v>300800</v>
@@ -2849,7 +2858,7 @@
         <v>12000</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2861,7 +2870,7 @@
         <v>4059192</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D8" s="1">
         <v>14</v>
@@ -2870,7 +2879,7 @@
         <v>101700</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G8" s="1">
         <v>9</v>
@@ -2885,13 +2894,13 @@
         <v>2000</v>
       </c>
       <c r="K8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L8">
         <v>4059219</v>
       </c>
       <c r="M8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N8">
         <v>300800</v>
@@ -2900,7 +2909,7 @@
         <v>12000</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2912,7 +2921,7 @@
         <v>4059193</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" s="1">
         <v>14</v>
@@ -2921,7 +2930,7 @@
         <v>101600</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G9" s="1">
         <v>9</v>
@@ -2936,13 +2945,13 @@
         <v>2000</v>
       </c>
       <c r="K9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L9">
         <v>4059219</v>
       </c>
       <c r="M9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N9">
         <v>300800</v>
@@ -2951,7 +2960,7 @@
         <v>12000</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2963,7 +2972,7 @@
         <v>4059194</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D10" s="1">
         <v>14</v>
@@ -2972,7 +2981,7 @@
         <v>105500</v>
       </c>
       <c r="F10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G10" s="1">
         <v>9</v>
@@ -2987,13 +2996,13 @@
         <v>2000</v>
       </c>
       <c r="K10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L10">
         <v>4059220</v>
       </c>
       <c r="M10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N10">
         <v>300800</v>
@@ -3002,7 +3011,7 @@
         <v>12000</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -3027,7 +3036,7 @@
         <v>4059191</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D5" s="1">
         <v>14</v>
@@ -3036,7 +3045,7 @@
         <v>102000</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G5" s="1">
         <v>9</v>
@@ -3051,19 +3060,19 @@
         <v>1000</v>
       </c>
       <c r="K5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L5">
         <v>4059217</v>
       </c>
       <c r="M5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:16">
@@ -3075,7 +3084,7 @@
         <v>4059192</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D6" s="1">
         <v>14</v>
@@ -3084,7 +3093,7 @@
         <v>102100</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G6" s="1">
         <v>9</v>
@@ -3099,19 +3108,19 @@
         <v>2000</v>
       </c>
       <c r="K6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L6">
         <v>4059218</v>
       </c>
       <c r="M6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:16">
@@ -3123,7 +3132,7 @@
         <v>4059193</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D7" s="1">
         <v>14</v>
@@ -3132,7 +3141,7 @@
         <v>101500</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G7" s="1">
         <v>9</v>
@@ -3147,19 +3156,19 @@
         <v>2000</v>
       </c>
       <c r="K7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L7">
         <v>4059219</v>
       </c>
       <c r="M7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:16">
@@ -3171,7 +3180,7 @@
         <v>4059194</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D8" s="1">
         <v>14</v>
@@ -3180,7 +3189,7 @@
         <v>103100</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G8" s="1">
         <v>9</v>
@@ -3195,19 +3204,19 @@
         <v>2000</v>
       </c>
       <c r="K8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L8">
         <v>4059220</v>
       </c>
       <c r="M8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
